--- a/download/DeepMindQ_Development_Tracking_Board.xlsx
+++ b/download/DeepMindQ_Development_Tracking_Board.xlsx
@@ -1102,7 +1102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:I20"/>
+  <dimension ref="B2:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1795,6 +1795,90 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Phase 1A: Intelligence Foundation</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>COMPLETE</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>IntelligenceNarrative real; Confidence real (4-factor); Evidence traceable; Action-driven; Command Center integrated; VP Sales 5Q validated; 1888 tests pass</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>product-baseline-v1 (c059d8c)</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>1 session (correction cycle + integration evidence)</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Established intelligence-first architecture. User approved closure 2026-08-02. Known limitation documented.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Phase 1B: Command Center Executive Intelligence Experience</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>PLANNING</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Experience blueprint reviewed; Component implementation plan approved; Anti-SaaS differentiation confirmed; Evidence standards met for all items</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Phase 1A COMPLETE; Design document reviewed and approved</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>TBD after design review</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>NOT a UI redesign. Objective: Transform Command Center into primary decision environment for VP Sales/CRO. Design document MUST be reviewed before any coding.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="B3:I3"/>
@@ -1810,7 +1894,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:J15"/>
+  <dimension ref="B2:J23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -2235,6 +2319,382 @@
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>PHASE-1A-CLOSE</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Phase 1A — Intelligence Foundation</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Phase 1A Official Closure Record</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Super Z</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>All 7 acceptance items verified; user formally approved closure</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1A-DEL-01</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Phase 1A — Intelligence Foundation</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>IntelligenceNarrative component — signal-driven narrative generation with real engine data</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Super Z</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Connected to intelligence-narrative-service.ts; progressive disclosure L1-L4</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1A-DEL-02</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Phase 1A — Intelligence Foundation</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>ConfidenceIndicator — multi-factor real computation (Signal 30% + Evidence 30% + Capability 25% + Data 15%)</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Super Z</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>computeConfidenceScore() verified with 4-dimension weighted formula; 20 tests pass</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>1A-DEL-03</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Phase 1A — Intelligence Foundation</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>EvidenceChain — connected to real evidence model via GroundingEngine</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Super Z</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>buildNarrativeEvidence() maps GroundingEngine output to UI evidence items</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>1A-DEL-04</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Phase 1A — Intelligence Foundation</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>IntelligenceCard / EvidenceChain / IntelligencePanel / ActionCTA — end-to-end connected</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Super Z</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Full intelligence-os component chain: data → narrative → confidence → evidence → action</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>1A-DEL-05</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Phase 1A — Intelligence Foundation</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Intelligence API layer — /api/intelligence/narratives endpoint with 3 modes</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Super Z</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>GET with limit/companyId/minConfidence; signal drill-down; confidence detail drill-down</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>1A-DEL-06</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Phase 1A — Intelligence Foundation</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Command Center page — consumes real intelligence pipeline (not template data)</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Super Z</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>command-center.tsx integrates useIntelligenceNarratives hook; real API consumption</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>1A-DEL-07</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Phase 1A — Intelligence Foundation</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Phase 1A test suite — 20 tests covering confidence, evidence, VP Sales 5-question validation</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Super Z</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1888 pass / 14 skip / 0 fail; tsc clean; lint clean; net +20 tests</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
